--- a/exports/VBL_full_report.xlsx
+++ b/exports/VBL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>3.7</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44585.55208333334</v>
+        <v>44586.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>119.8</v>
+        <v>115.95</v>
       </c>
       <c r="I2" t="n">
         <v>117.8208297636547</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>5.74</v>
+        <v>2.34</v>
       </c>
       <c r="L2" t="n">
         <v>1.24</v>
       </c>
       <c r="M2" t="n">
-        <v>0.65</v>
+        <v>0.96</v>
       </c>
       <c r="N2" t="n">
         <v>2.96</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>8.59</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>122.65</v>
+        <v>124.35</v>
       </c>
       <c r="I3" t="n">
         <v>124.2501983836162</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.78</v>
+        <v>-7.24</v>
       </c>
       <c r="L3" t="n">
-        <v>5.99</v>
+        <v>7.81</v>
       </c>
       <c r="M3" t="n">
         <v>0.66</v>
       </c>
       <c r="N3" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="O3" t="n">
         <v>-2.96</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>7.71</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44615.55208333334</v>
+        <v>44616.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>122.8</v>
+        <v>118.4</v>
       </c>
       <c r="I4" t="n">
         <v>118.6583626367196</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.25</v>
+        <v>-4.78</v>
       </c>
       <c r="L4" t="n">
-        <v>4.95</v>
+        <v>5.23</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>3.91</v>
       </c>
       <c r="N4" t="n">
-        <v>3.64</v>
+        <v>3.91</v>
       </c>
       <c r="O4" t="n">
         <v>2.28</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>8.91</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44620.55208333334</v>
+        <v>44622.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>125.85</v>
+        <v>132.65</v>
       </c>
       <c r="I5" t="n">
         <v>127.2701973575627</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.29</v>
+        <v>-12.04</v>
       </c>
       <c r="L5" t="n">
-        <v>7.09</v>
+        <v>14.27</v>
       </c>
       <c r="M5" t="n">
         <v>0.21</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.81</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44631.55208333334</v>
+        <v>44634.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>120.9</v>
+        <v>119.6</v>
       </c>
       <c r="I6" t="n">
         <v>120.0291958039896</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.859999999999999</v>
+        <v>-9.84</v>
       </c>
       <c r="L6" t="n">
         <v>11.91</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>8.77</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44641.55208333334</v>
+        <v>44642.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>125.3</v>
+        <v>130.4</v>
       </c>
       <c r="I7" t="n">
         <v>129.1700941479845</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.77</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>7.69</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M7" t="n">
         <v>1.47</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.13</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>198</v>
+        <v>189.4</v>
       </c>
       <c r="I8" t="n">
         <v>194.1952946708316</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>150.1666666666667</v>
+        <v>153</v>
       </c>
       <c r="K8" t="n">
-        <v>51.84</v>
+        <v>45.25</v>
       </c>
       <c r="L8" t="n">
         <v>5.44</v>
@@ -897,7 +992,7 @@
         <v>3.37</v>
       </c>
       <c r="N8" t="n">
-        <v>4.94</v>
+        <v>6.87</v>
       </c>
       <c r="O8" t="n">
         <v>2.15</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>208</v>
+        <v>209</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>11.37</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44797.38541666666</v>
+        <v>44797.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>199.3</v>
+        <v>204.5</v>
       </c>
       <c r="I9" t="n">
         <v>203.1809397425273</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.23</v>
+        <v>-7.97</v>
       </c>
       <c r="L9" t="n">
-        <v>5.6</v>
+        <v>10.24</v>
       </c>
       <c r="M9" t="n">
         <v>0.71</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.81</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44830.38541666666</v>
+        <v>44830.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>219.75</v>
+        <v>214</v>
       </c>
       <c r="I10" t="n">
         <v>216.9434204909963</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>32.83333333333334</v>
+        <v>33</v>
       </c>
       <c r="K10" t="n">
-        <v>7.46</v>
+        <v>4.65</v>
       </c>
       <c r="L10" t="n">
         <v>6.11</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.51</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.38541666666</v>
+        <v>44838.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>218.85</v>
+        <v>226.8</v>
       </c>
       <c r="I11" t="n">
         <v>223.5677527436154</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.27</v>
+        <v>-5.98</v>
       </c>
       <c r="L11" t="n">
-        <v>2.78</v>
+        <v>7.94</v>
       </c>
       <c r="M11" t="n">
         <v>2.34</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>9.43</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44845.38541666666</v>
+        <v>44845.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>210.9</v>
+        <v>209.2</v>
       </c>
       <c r="I12" t="n">
         <v>209.9370045666124</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>-7.01</v>
+        <v>-7.76</v>
       </c>
       <c r="L12" t="n">
-        <v>7.05</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>2.18</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.56</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44865.55208333334</v>
+        <v>44866.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>209.7</v>
+        <v>217</v>
       </c>
       <c r="I13" t="n">
         <v>216.0263411315836</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.24</v>
+        <v>-3.73</v>
       </c>
       <c r="L13" t="n">
         <v>5.07</v>
@@ -1182,7 +1337,7 @@
         <v>1.99</v>
       </c>
       <c r="N13" t="n">
-        <v>2.23</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
         <v>-3.86</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.69</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44879.38541666666</v>
+        <v>44879.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>222.55</v>
+        <v>216.6</v>
       </c>
       <c r="I14" t="n">
         <v>217.958548044927</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>2.56</v>
+        <v>-0.18</v>
       </c>
       <c r="L14" t="n">
         <v>2.95</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>11.33</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44895.38541666666</v>
+        <v>44895.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>239.05</v>
+        <v>261.8</v>
       </c>
       <c r="I15" t="n">
         <v>239.2272744184714</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.36</v>
+        <v>-20.87</v>
       </c>
       <c r="L15" t="n">
-        <v>10.71</v>
+        <v>21.93</v>
       </c>
       <c r="M15" t="n">
         <v>0.75</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>15.71</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44930.55208333334</v>
+        <v>44931.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>261.2</v>
+        <v>255.8</v>
       </c>
       <c r="I16" t="n">
         <v>257.3625349743665</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.23</v>
+        <v>-2.29</v>
       </c>
       <c r="L16" t="n">
         <v>11.92</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>9.15</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44963.55208333334</v>
+        <v>44964.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>244.35</v>
+        <v>257.5</v>
       </c>
       <c r="I17" t="n">
         <v>245.8736126413861</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K17" t="n">
-        <v>4.48</v>
+        <v>-0.66</v>
       </c>
       <c r="L17" t="n">
         <v>4.07</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
         <v>6.34</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>12.02</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45000.55208333334</v>
+        <v>45001.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>269</v>
+        <v>258.1</v>
       </c>
       <c r="I18" t="n">
         <v>260.0803944527356</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K18" t="n">
-        <v>4.47</v>
+        <v>0.23</v>
       </c>
       <c r="L18" t="n">
         <v>4.08</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>9.02</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>276.85</v>
+        <v>279.6</v>
       </c>
       <c r="I19" t="n">
         <v>279.2977451242042</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.26</v>
+        <v>-8.33</v>
       </c>
       <c r="L19" t="n">
-        <v>8.1</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>1.27</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.7</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45084.55208333334</v>
+        <v>45085.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>330</v>
+        <v>316.6</v>
       </c>
       <c r="I20" t="n">
         <v>321.5631962211127</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>65.16666666666667</v>
+        <v>66</v>
       </c>
       <c r="K20" t="n">
-        <v>18.03</v>
+        <v>13.23</v>
       </c>
       <c r="L20" t="n">
         <v>1.65</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.02</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45148.55208333334</v>
+        <v>45149.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>328</v>
+        <v>338.15</v>
       </c>
       <c r="I21" t="n">
         <v>333.4993069242468</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.6</v>
+        <v>-6.81</v>
       </c>
       <c r="L21" t="n">
         <v>103.54</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.14</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45202.55208333334</v>
+        <v>45203.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="I22" t="n">
         <v>370.0758145816067</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K22" t="n">
-        <v>10.01</v>
+        <v>8.83</v>
       </c>
       <c r="L22" t="n">
         <v>2.91</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.46</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45225.55208333334</v>
+        <v>45226.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>350.8</v>
+        <v>367.3</v>
       </c>
       <c r="I23" t="n">
         <v>365.0521111921836</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K23" t="n">
-        <v>4.67</v>
+        <v>0.19</v>
       </c>
       <c r="L23" t="n">
         <v>3.37</v>
@@ -1752,7 +2027,7 @@
         <v>1.29</v>
       </c>
       <c r="N23" t="n">
-        <v>1.11</v>
+        <v>4.48</v>
       </c>
       <c r="O23" t="n">
         <v>-0.97</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.32</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45349.55208333334</v>
+        <v>45350.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>588</v>
+        <v>565.8</v>
       </c>
       <c r="I24" t="n">
         <v>583.7369979113237</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>123.1666666666667</v>
+        <v>124</v>
       </c>
       <c r="K24" t="n">
-        <v>60.09</v>
+        <v>54.04</v>
       </c>
       <c r="L24" t="n">
         <v>4.49</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>9.09</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45384.55208333334</v>
+        <v>45385.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>564.75</v>
+        <v>584.55</v>
       </c>
       <c r="I25" t="n">
         <v>582.1861638866723</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K25" t="n">
-        <v>0.19</v>
+        <v>-3.31</v>
       </c>
       <c r="L25" t="n">
         <v>5.69</v>
@@ -1866,7 +2165,7 @@
         <v>1.75</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>4.26</v>
       </c>
       <c r="O25" t="n">
         <v>-4.15</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>7.88</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45392.55208333334</v>
+        <v>45394.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>570.8</v>
+        <v>560</v>
       </c>
       <c r="I26" t="n">
         <v>569.9004328991122</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.35</v>
+        <v>-4.2</v>
       </c>
       <c r="L26" t="n">
         <v>5.12</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>6.77</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45407.55208333334</v>
+        <v>45408.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>576.85</v>
+        <v>582</v>
       </c>
       <c r="I27" t="n">
         <v>580.364329261733</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.01</v>
+        <v>-3.93</v>
       </c>
       <c r="L27" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
         <v>1.52</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>5.52</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45422.55208333334</v>
+        <v>45425.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>585.6</v>
+        <v>572.95</v>
       </c>
       <c r="I28" t="n">
         <v>574.5554914605003</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K28" t="n">
-        <v>0.62</v>
+        <v>-1.55</v>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="M28" t="n">
         <v>0.39</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.26</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45448.55208333334</v>
+        <v>45449.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>597.4</v>
+        <v>600.35</v>
       </c>
       <c r="I29" t="n">
         <v>599.317722810219</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.27</v>
+        <v>-4.78</v>
       </c>
       <c r="L29" t="n">
         <v>8.84</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.57</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>625.45</v>
+        <v>618.75</v>
       </c>
       <c r="I30" t="n">
         <v>618.9763679563222</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K30" t="n">
-        <v>4.18</v>
+        <v>3.06</v>
       </c>
       <c r="L30" t="n">
         <v>0.32</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>5.02</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45497.55208333334</v>
+        <v>45498.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>643.2</v>
+        <v>658.7</v>
       </c>
       <c r="I31" t="n">
         <v>649.8101274872096</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.95</v>
+        <v>-6.46</v>
       </c>
       <c r="L31" t="n">
-        <v>4.74</v>
+        <v>6.59</v>
       </c>
       <c r="M31" t="n">
         <v>0.58</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>7.39</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45502.55208333334</v>
+        <v>45503.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>674.8</v>
+        <v>631.65</v>
       </c>
       <c r="I32" t="n">
         <v>639.3551349407779</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>2.44</v>
+        <v>-4.11</v>
       </c>
       <c r="L32" t="n">
-        <v>2.78</v>
+        <v>4.36</v>
       </c>
       <c r="M32" t="n">
         <v>-0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="O32" t="n">
         <v>2.94</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.08</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45524.55208333334</v>
+        <v>45525.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>597</v>
+        <v>613.55</v>
       </c>
       <c r="I33" t="n">
         <v>608.8377663903545</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K33" t="n">
-        <v>5.49</v>
+        <v>2.87</v>
       </c>
       <c r="L33" t="n">
         <v>7.64</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.57</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45565.38541666666</v>
+        <v>45565.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>607.95</v>
+        <v>607.75</v>
       </c>
       <c r="I34" t="n">
         <v>607.8349775101681</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.91</v>
+        <v>-0.95</v>
       </c>
       <c r="L34" t="n">
         <v>10.49</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.23</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45573.38541666666</v>
+        <v>45573.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>581.15</v>
+        <v>591</v>
       </c>
       <c r="I35" t="n">
         <v>589.9480473872185</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K35" t="n">
-        <v>4.38</v>
+        <v>2.76</v>
       </c>
       <c r="L35" t="n">
         <v>1.69</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>10.89</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45609.38541666666</v>
+        <v>45609.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>573.8</v>
+        <v>573</v>
       </c>
       <c r="I36" t="n">
         <v>573.0755894512261</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>35.83333333333334</v>
+        <v>36</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.91</v>
+        <v>-3.05</v>
       </c>
       <c r="L36" t="n">
-        <v>4.11</v>
+        <v>4.4</v>
       </c>
       <c r="M36" t="n">
         <v>3.3</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>6.49</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45614.38541666666</v>
+        <v>45614.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>596.3</v>
+        <v>611.9</v>
       </c>
       <c r="I37" t="n">
         <v>610.1932417068872</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.07</v>
+        <v>-6.79</v>
       </c>
       <c r="L37" t="n">
-        <v>4.57</v>
+        <v>7.78</v>
       </c>
       <c r="M37" t="n">
         <v>2.44</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45646.38541666666</v>
+        <v>45646.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>621.35</v>
+        <v>615.8</v>
       </c>
       <c r="I38" t="n">
         <v>620.4324055891632</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>31.83333333333333</v>
+        <v>32</v>
       </c>
       <c r="K38" t="n">
-        <v>1.54</v>
+        <v>0.64</v>
       </c>
       <c r="L38" t="n">
         <v>3.06</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>5.49</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45658.38541666666</v>
+        <v>45658.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>645.1</v>
+        <v>650</v>
       </c>
       <c r="I39" t="n">
         <v>649.5394510378866</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.76</v>
+        <v>-5.55</v>
       </c>
       <c r="L39" t="n">
         <v>7.5</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>5.03</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45663.55208333334</v>
+        <v>45664.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>630.15</v>
+        <v>617.8</v>
       </c>
       <c r="I40" t="n">
         <v>622.7195534483769</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.05</v>
+        <v>-4.95</v>
       </c>
       <c r="L40" t="n">
-        <v>3.79</v>
+        <v>5.38</v>
       </c>
       <c r="M40" t="n">
         <v>1.03</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.37</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45688.55208333334</v>
+        <v>45689.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>538</v>
+        <v>565.45</v>
       </c>
       <c r="I41" t="n">
         <v>560.64848986729</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K41" t="n">
-        <v>12.92</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="L41" t="n">
         <v>3.09</v>
@@ -2778,7 +3269,7 @@
         <v>1.48</v>
       </c>
       <c r="N41" t="n">
-        <v>3.24</v>
+        <v>4.37</v>
       </c>
       <c r="O41" t="n">
         <v>-1.77</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>8.26</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45695.55208333334</v>
+        <v>45698.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>554</v>
+        <v>540.25</v>
       </c>
       <c r="I42" t="n">
         <v>547.8191262881771</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.02</v>
+        <v>-4.46</v>
       </c>
       <c r="L42" t="n">
-        <v>4.67</v>
+        <v>5.79</v>
       </c>
       <c r="M42" t="n">
         <v>0.27</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.27</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>476</v>
+        <v>486.7</v>
       </c>
       <c r="I43" t="n">
         <v>483.4656706450481</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>11.89</v>
+        <v>9.91</v>
       </c>
       <c r="L43" t="n">
         <v>3.86</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>10.03</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>536.65</v>
+        <v>510</v>
       </c>
       <c r="I44" t="n">
         <v>513.4287724946205</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K44" t="n">
-        <v>10.26</v>
+        <v>4.79</v>
       </c>
       <c r="L44" t="n">
         <v>3.33</v>
       </c>
       <c r="M44" t="n">
-        <v>0.67</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="N44" t="n">
         <v>2.54</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>6.86</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45758.38541666666</v>
+        <v>45758.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>543.75</v>
+        <v>546.65</v>
       </c>
       <c r="I45" t="n">
         <v>545.0020065884095</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.62</v>
+        <v>-7.19</v>
       </c>
       <c r="L45" t="n">
         <v>7.77</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>7.09</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45771.55208333334</v>
+        <v>45772.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>532.9</v>
+        <v>520.65</v>
       </c>
       <c r="I46" t="n">
         <v>525.060180490723</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.52</v>
+        <v>-4.76</v>
       </c>
       <c r="L46" t="n">
-        <v>2.86</v>
+        <v>5.59</v>
       </c>
       <c r="M46" t="n">
         <v>0.36</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.77</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45853.55208333334</v>
+        <v>45854.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>470</v>
+        <v>479.25</v>
       </c>
       <c r="I47" t="n">
         <v>470.1330592680707</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>81.16666666666667</v>
+        <v>82</v>
       </c>
       <c r="K47" t="n">
-        <v>9.73</v>
+        <v>7.95</v>
       </c>
       <c r="L47" t="n">
         <v>4.43</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.65</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45897.55208333334</v>
+        <v>45898.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>495.25</v>
+        <v>490</v>
       </c>
       <c r="I48" t="n">
         <v>494.3868444573114</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K48" t="n">
-        <v>3.34</v>
+        <v>2.24</v>
       </c>
       <c r="L48" t="n">
         <v>2.98</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.92</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45945.55208333334</v>
+        <v>45946.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>445.3</v>
+        <v>461.3</v>
       </c>
       <c r="I49" t="n">
         <v>450.893859746324</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K49" t="n">
-        <v>9.119999999999999</v>
+        <v>5.86</v>
       </c>
       <c r="L49" t="n">
         <v>4.83</v>
@@ -3234,7 +3821,7 @@
         <v>1.28</v>
       </c>
       <c r="N49" t="n">
-        <v>2.91</v>
+        <v>3.65</v>
       </c>
       <c r="O49" t="n">
         <v>-1.95</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.89</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45971.38541666666</v>
+        <v>45971.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="I50" t="n">
         <v>467.5500347574464</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>1.67</v>
+        <v>0.37</v>
       </c>
       <c r="L50" t="n">
         <v>3.46</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.54</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45986.55208333334</v>
+        <v>45987.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>447.95</v>
+        <v>465.05</v>
       </c>
       <c r="I51" t="n">
         <v>462.3304186843114</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>3.25</v>
+        <v>-0.44</v>
       </c>
       <c r="L51" t="n">
         <v>2.1</v>
@@ -3348,7 +3959,7 @@
         <v>0.77</v>
       </c>
       <c r="N51" t="n">
-        <v>1.7</v>
+        <v>3.91</v>
       </c>
       <c r="O51" t="n">
         <v>-1.76</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>6.03</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46042.55208333334</v>
+        <v>46043.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>488</v>
+        <v>479.75</v>
       </c>
       <c r="I52" t="n">
         <v>484.4188098512765</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K52" t="n">
-        <v>4.93</v>
+        <v>3.16</v>
       </c>
       <c r="L52" t="n">
         <v>3.94</v>
       </c>
       <c r="M52" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="N52" t="n">
         <v>2.51</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>5.69</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>401.75</v>
+        <v>418.3</v>
       </c>
       <c r="I53" t="n">
         <v>412.4009003976929</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>76.16666666666667</v>
+        <v>77</v>
       </c>
       <c r="K53" t="n">
-        <v>16.26</v>
+        <v>12.81</v>
       </c>
       <c r="L53" t="n">
         <v>2.58</v>
@@ -3462,7 +4097,7 @@
         <v>3.33</v>
       </c>
       <c r="N53" t="n">
-        <v>4.49</v>
+        <v>5.54</v>
       </c>
       <c r="O53" t="n">
         <v>-1.84</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.84</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46155.38541666666</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>497.2</v>
+        <v>489</v>
       </c>
       <c r="I54" t="n">
         <v>489.2100178808716</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K54" t="n">
-        <v>18.86</v>
+        <v>16.9</v>
       </c>
       <c r="L54" t="n">
         <v>1.73</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>6.53</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46162.55208333334</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>514</v>
+        <v>524.45</v>
       </c>
       <c r="I55" t="n">
         <v>520.9520418653858</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.11</v>
+        <v>-7.25</v>
       </c>
       <c r="L55" t="n">
-        <v>6.1</v>
+        <v>7.55</v>
       </c>
       <c r="M55" t="n">
         <v>0.49</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>5.89</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46192.55208333334</v>
+        <v>46195.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>529.9</v>
+        <v>510.9</v>
       </c>
       <c r="I56" t="n">
         <v>518.948215035402</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K56" t="n">
-        <v>1.04</v>
+        <v>-2.58</v>
       </c>
       <c r="L56" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="M56" t="n">
         <v>1.14</v>
       </c>
       <c r="N56" t="n">
-        <v>2.37</v>
+        <v>3.38</v>
       </c>
       <c r="O56" t="n">
         <v>1.17</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.92</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46281.55208333334</v>
+        <v>46282.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>412.55</v>
+        <v>418.6</v>
       </c>
       <c r="I57" t="n">
         <v>417.4022307878422</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>86.16666666666667</v>
+        <v>87</v>
       </c>
       <c r="K57" t="n">
-        <v>19.25</v>
+        <v>18.07</v>
       </c>
       <c r="L57" t="n">
         <v>3.74</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.23</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46311.55208333334</v>
+        <v>46314.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>430.7</v>
+        <v>421.9</v>
       </c>
       <c r="I58" t="n">
         <v>423.3034383106543</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K58" t="n">
-        <v>2.89</v>
+        <v>0.79</v>
       </c>
       <c r="L58" t="n">
         <v>1.82</v>
@@ -3747,7 +4442,7 @@
         <v>0.88</v>
       </c>
       <c r="N58" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="O58" t="n">
         <v>1.21</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3807,6 +4514,12 @@
       <c r="Q59" t="n">
         <v>12</v>
       </c>
+      <c r="R59" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5909,7 +6622,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.6</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="6">
@@ -5919,7 +6632,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -5929,7 +6642,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>150.2</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8">
@@ -5939,7 +6652,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5949,7 +6662,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -5959,7 +6672,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="11">
@@ -5969,7 +6682,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -5979,7 +6692,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -5989,7 +6702,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>63.2</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="14">
@@ -5999,7 +6712,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.59</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15">
@@ -6009,7 +6722,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.24</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="16">
@@ -6019,7 +6732,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.86</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="17">
@@ -6029,7 +6742,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>60.09</v>
+        <v>54.04</v>
       </c>
     </row>
     <row r="18">
@@ -6039,7 +6752,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.4</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="19">
@@ -6049,7 +6762,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.5</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="20">
@@ -6059,7 +6772,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.11</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="21">
@@ -6079,7 +6792,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -6089,7 +6802,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -6099,7 +6812,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="25">
@@ -6109,7 +6822,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.03</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -6119,7 +6832,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.83</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="27">
@@ -6139,7 +6852,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
